--- a/data/trans_dic/P43E-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P43E-Habitat-trans_dic.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,19%</t>
         </is>
       </c>
     </row>
@@ -635,32 +635,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,27; 20,9</t>
+          <t>13,53; 20,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,45; 15,76</t>
+          <t>8,42; 15,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,41; 17,01</t>
+          <t>10,31; 16,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13,27; 20,9</t>
+          <t>13,53; 20,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,45; 15,76</t>
+          <t>8,42; 15,28</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,41; 17,01</t>
+          <t>10,31; 16,88</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>21,17%</t>
         </is>
       </c>
     </row>
@@ -715,32 +715,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>21,3; 28,4</t>
+          <t>21,25; 28,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,49; 18,35</t>
+          <t>12,47; 18,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17,69; 24,26</t>
+          <t>17,71; 24,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21,3; 28,4</t>
+          <t>21,25; 28,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,49; 18,35</t>
+          <t>12,47; 18,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,69; 24,26</t>
+          <t>17,71; 24,73</t>
         </is>
       </c>
     </row>
@@ -767,7 +767,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>31,22%</t>
         </is>
       </c>
     </row>
@@ -795,32 +795,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21,23; 29,6</t>
+          <t>21,02; 29,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,58; 21,48</t>
+          <t>14,24; 21,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19,86; 34,5</t>
+          <t>27,25; 36,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21,23; 29,6</t>
+          <t>21,02; 29,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,58; 21,48</t>
+          <t>14,24; 21,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,86; 34,5</t>
+          <t>27,25; 36,0</t>
         </is>
       </c>
     </row>
@@ -847,7 +847,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>28,71%</t>
         </is>
       </c>
     </row>
@@ -875,32 +875,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>20,19; 27,05</t>
+          <t>20,17; 27,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,74; 22,16</t>
+          <t>15,99; 22,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,93; 29,61</t>
+          <t>25,45; 31,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20,19; 27,05</t>
+          <t>20,17; 27,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>15,74; 22,16</t>
+          <t>15,99; 22,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,93; 29,61</t>
+          <t>25,45; 31,95</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>24,55%</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>21,08; 24,84</t>
+          <t>21,27; 24,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14,83; 17,99</t>
+          <t>14,8; 18,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19,17; 25,19</t>
+          <t>22,7; 26,4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21,08; 24,84</t>
+          <t>21,27; 24,87</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,83; 17,99</t>
+          <t>14,8; 18,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,17; 25,19</t>
+          <t>22,7; 26,4</t>
         </is>
       </c>
     </row>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35712</t>
+          <t>37638</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35712</t>
+          <t>37638</t>
         </is>
       </c>
     </row>
@@ -1180,32 +1180,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>56792; 89436</t>
+          <t>57907; 89742</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>29475; 54976</t>
+          <t>29360; 53302</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27850; 45483</t>
+          <t>29433; 48191</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>56792; 89436</t>
+          <t>57907; 89742</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>29475; 54976</t>
+          <t>29360; 53302</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27850; 45483</t>
+          <t>29433; 48191</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>79033</t>
+          <t>89468</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79033</t>
+          <t>89468</t>
         </is>
       </c>
     </row>
@@ -1298,32 +1298,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>139172; 185545</t>
+          <t>138825; 185793</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>78866; 115825</t>
+          <t>78749; 114452</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>67308; 92283</t>
+          <t>74848; 104497</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>139172; 185545</t>
+          <t>138825; 185793</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>78866; 115825</t>
+          <t>78749; 114452</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>67308; 92283</t>
+          <t>74848; 104497</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>104131</t>
+          <t>115376</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>104131</t>
+          <t>115376</t>
         </is>
       </c>
     </row>
@@ -1416,32 +1416,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>111283; 155195</t>
+          <t>110211; 155377</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>72059; 106171</t>
+          <t>70413; 105437</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>70305; 122105</t>
+          <t>100698; 133047</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>111283; 155195</t>
+          <t>110211; 155377</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>72059; 106171</t>
+          <t>70413; 105437</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>70305; 122105</t>
+          <t>100698; 133047</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>141134</t>
+          <t>152723</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>141134</t>
+          <t>152723</t>
         </is>
       </c>
     </row>
@@ -1534,32 +1534,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>129951; 174041</t>
+          <t>129789; 175778</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>106878; 150533</t>
+          <t>108634; 151436</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>96337; 168453</t>
+          <t>135411; 169968</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>129951; 174041</t>
+          <t>129789; 175778</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>106878; 150533</t>
+          <t>108634; 151436</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>96337; 168453</t>
+          <t>135411; 169968</t>
         </is>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>360010</t>
+          <t>395204</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>360010</t>
+          <t>395204</t>
         </is>
       </c>
     </row>
@@ -1652,32 +1652,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>474104; 558644</t>
+          <t>478474; 559306</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>319342; 387366</t>
+          <t>318740; 387912</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>301053; 395733</t>
+          <t>365309; 424889</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>474104; 558644</t>
+          <t>478474; 559306</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>319342; 387366</t>
+          <t>318740; 387912</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>301053; 395733</t>
+          <t>365309; 424889</t>
         </is>
       </c>
     </row>
